--- a/web/data/university_fee_with_latlon.xlsx
+++ b/web/data/university_fee_with_latlon.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="135">
   <si>
     <t>คำค้น</t>
   </si>
@@ -329,9 +329,6 @@
   </si>
   <si>
     <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ (วศ.บ. (วิศวกรรมคอมพิวเตอร์))</t>
-  </si>
-  <si>
-    <t>คณะวิศวกรรมศาสคร์</t>
   </si>
   <si>
     <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ) (วศ.บ. (วิศวกรรมคอมพิวเตอร์))</t>
@@ -440,13 +437,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -829,9 +826,9 @@
   <cols>
     <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="7" width="52.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="38.14785714285715" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="98.57642857142856" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -999,7 +996,7 @@
         <v>100.5007596</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1031,7 +1028,7 @@
         <v>98.3529461</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1063,7 +1060,7 @@
         <v>100.7829827</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1095,7 +1092,7 @@
         <v>100.7829827</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1127,7 +1124,7 @@
         <v>100.7829827</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
@@ -1159,7 +1156,7 @@
         <v>104.9194652</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -1191,7 +1188,7 @@
         <v>99.8973838530508</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1223,7 +1220,7 @@
         <v>100.6014053</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -1255,7 +1252,7 @@
         <v>102.8635325225</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
@@ -1287,7 +1284,7 @@
         <v>100.5604071</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -1319,7 +1316,7 @@
         <v>100.8562082</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
@@ -1351,7 +1348,7 @@
         <v>100.5317945</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>58</v>
       </c>
@@ -1383,7 +1380,7 @@
         <v>100.5328752</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>58</v>
       </c>
@@ -1415,7 +1412,7 @@
         <v>100.5328752</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>58</v>
       </c>
@@ -2287,13 +2284,13 @@
         <v>103</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>15</v>
@@ -2316,16 +2313,16 @@
         <v>58</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="D47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>20</v>
@@ -2348,16 +2345,16 @@
         <v>58</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>80</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>20</v>
@@ -2380,10 +2377,10 @@
         <v>58</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>26</v>
@@ -2412,7 +2409,7 @@
         <v>58</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>79</v>
@@ -2444,16 +2441,16 @@
         <v>58</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>20</v>
@@ -2476,13 +2473,13 @@
         <v>58</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="D52" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>26</v>
@@ -2508,7 +2505,7 @@
         <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>12</v>
@@ -2540,16 +2537,16 @@
         <v>58</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>20</v>
@@ -2572,7 +2569,7 @@
         <v>58</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>12</v>
@@ -2604,16 +2601,16 @@
         <v>58</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>124</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>20</v>
@@ -2668,7 +2665,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>56</v>
@@ -2677,7 +2674,7 @@
         <v>26</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>20</v>
@@ -2700,7 +2697,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>56</v>
@@ -2732,10 +2729,10 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>26</v>
@@ -2764,10 +2761,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>26</v>
@@ -2796,10 +2793,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>26</v>
@@ -2828,7 +2825,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>12</v>
@@ -2860,7 +2857,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>12</v>

--- a/web/data/university_fee_with_latlon.xlsx
+++ b/web/data/university_fee_with_latlon.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="133">
   <si>
     <t>คำค้น</t>
   </si>
@@ -145,7 +145,7 @@
     <t>มหาวิทยาลัยวลัยลักษณ์</t>
   </si>
   <si>
-    <t>วิศวกรรมศาสตร์และเทคโนโลยี</t>
+    <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี</t>
   </si>
   <si>
     <t>วิศวกรรมศาสตรบัณฑิต สาขาวิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
@@ -175,16 +175,10 @@
     <t>มหาวิทยาลัยเทคโนโลยีมหานคร</t>
   </si>
   <si>
-    <t>วิศวกรรมศาสตร์</t>
-  </si>
-  <si>
     <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
   </si>
   <si>
     <t>สถาบันการจัดการปัญญาภิวัฒน์ แจ้งวัฒนะ นนทบุรี</t>
-  </si>
-  <si>
-    <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี</t>
   </si>
   <si>
     <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
@@ -836,7 +830,7 @@
     <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -900,7 +894,7 @@
         <v>100.5328752</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -932,7 +926,7 @@
         <v>102.8119933</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -964,7 +958,7 @@
         <v>98.9521552</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -1292,13 +1286,13 @@
         <v>52</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>20</v>
@@ -1321,16 +1315,16 @@
         <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>20</v>
@@ -1350,7 +1344,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>11</v>
@@ -1362,7 +1356,7 @@
         <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>20</v>
@@ -1382,7 +1376,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>11</v>
@@ -1394,7 +1388,7 @@
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>20</v>
@@ -1414,10 +1408,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>12</v>
@@ -1426,7 +1420,7 @@
         <v>26</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>20</v>
@@ -1446,19 +1440,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>20</v>
@@ -1478,19 +1472,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>20</v>
@@ -1499,7 +1493,7 @@
         <v>29100</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I21" s="6">
         <v>13.1202798</v>
@@ -1510,19 +1504,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>20</v>
@@ -1542,7 +1536,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>17</v>
@@ -1554,7 +1548,7 @@
         <v>26</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>20</v>
@@ -1574,7 +1568,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>22</v>
@@ -1586,7 +1580,7 @@
         <v>26</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>20</v>
@@ -1606,10 +1600,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>12</v>
@@ -1618,7 +1612,7 @@
         <v>26</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>20</v>
@@ -1638,19 +1632,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="D26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>15</v>
@@ -1670,10 +1664,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>12</v>
@@ -1682,7 +1676,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>20</v>
@@ -1702,19 +1696,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>20</v>
@@ -1734,22 +1728,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="G29" s="5">
         <v>35000</v>
@@ -1766,10 +1760,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>12</v>
@@ -1778,7 +1772,7 @@
         <v>26</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>20</v>
@@ -1798,7 +1792,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>25</v>
@@ -1810,7 +1804,7 @@
         <v>26</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>20</v>
@@ -1830,10 +1824,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>12</v>
@@ -1842,7 +1836,7 @@
         <v>26</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>15</v>
@@ -1862,19 +1856,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>20</v>
@@ -1894,10 +1888,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>12</v>
@@ -1906,7 +1900,7 @@
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>20</v>
@@ -1926,7 +1920,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>33</v>
@@ -1938,7 +1932,7 @@
         <v>26</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>20</v>
@@ -1958,7 +1952,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>33</v>
@@ -1970,7 +1964,7 @@
         <v>26</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>15</v>
@@ -1990,7 +1984,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>33</v>
@@ -2002,7 +1996,7 @@
         <v>26</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>20</v>
@@ -2022,19 +2016,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>20</v>
@@ -2054,13 +2048,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>26</v>
@@ -2086,10 +2080,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>12</v>
@@ -2098,7 +2092,7 @@
         <v>26</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>20</v>
@@ -2118,19 +2112,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>20</v>
@@ -2150,13 +2144,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>26</v>
@@ -2182,19 +2176,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>20</v>
@@ -2214,19 +2208,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>20</v>
@@ -2246,10 +2240,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>12</v>
@@ -2258,7 +2252,7 @@
         <v>26</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>20</v>
@@ -2278,19 +2272,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>15</v>
@@ -2310,19 +2304,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>20</v>
@@ -2342,19 +2336,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>20</v>
@@ -2374,19 +2368,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>20</v>
@@ -2406,19 +2400,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>20</v>
@@ -2438,19 +2432,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>20</v>
@@ -2470,16 +2464,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>26</v>
@@ -2502,10 +2496,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>12</v>
@@ -2534,10 +2528,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>12</v>
@@ -2546,7 +2540,7 @@
         <v>26</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>20</v>
@@ -2566,10 +2560,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>12</v>
@@ -2578,7 +2572,7 @@
         <v>26</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>20</v>
@@ -2598,10 +2592,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>12</v>
@@ -2610,7 +2604,7 @@
         <v>26</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>20</v>
@@ -2630,7 +2624,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>45</v>
@@ -2642,7 +2636,7 @@
         <v>26</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>20</v>
@@ -2662,19 +2656,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>20</v>
@@ -2694,19 +2688,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>20</v>
@@ -2726,19 +2720,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>20</v>
@@ -2758,19 +2752,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>20</v>
@@ -2790,19 +2784,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>20</v>
@@ -2822,10 +2816,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>12</v>
@@ -2834,7 +2828,7 @@
         <v>26</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>20</v>
@@ -2854,10 +2848,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>12</v>
@@ -2866,7 +2860,7 @@
         <v>26</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>20</v>
